--- a/static/nmck_template.xlsx
+++ b/static/nmck_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\мои\my_bot\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amira\Desktop\my_bot\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{716737F7-1335-4B2B-B918-40B9F11D578F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5290AF88-B066-4B50-A0DC-ABBDA9373DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>п/п №</t>
   </si>
@@ -46,6 +46,12 @@
   </si>
   <si>
     <t>Коммерческое предложение 1 от __________ Вх. № ____</t>
+  </si>
+  <si>
+    <t>Коммерческое предложение 2 от __________ Вх. № ____</t>
+  </si>
+  <si>
+    <t>Коммерческое предложение 3 от __________ Вх. № ____</t>
   </si>
 </sst>
 </file>
@@ -414,14 +420,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="21.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="21.25" customWidth="1"/>
+    <col min="8" max="8" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="67.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -441,13 +447,13 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
